--- a/Тест2/100.xlsx
+++ b/Тест2/100.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Qon va orqa miya suyuqligi</t>
   </si>
   <si>
-    <t xml:space="preserve">To'g'ri javob: Vaginal va rektal surtma. B guruh streptokokkni aniqlash uchun tug'ishdan oldingi kunlarda vaginal va rektal surtma olinadi. Manba: Mavzu materiali (100.docx); CDC. Guideline for Disinfection and Sterilization in Healthcare Facilities (2008).</t>
+    <t xml:space="preserve">To'g'ri javob: Vaginal va rektal surtma. B guruh streptokokkni aniqlash uchun tug'ishdan oldingi kunlarda vaginal va rektal surtma olinadi. Manba: Mavzu materiali (100.docx); CDC. Prevention of Perinatal Group B Streptococcal Disease: Revised Guidelines (MMWR 2010;59(RR-10)).</t>
   </si>
   <si>
     <t xml:space="preserve">Meningit gumon qilinganda streptokokk tekshiruvi uchun qaysi material olinadi?</t>
